--- a/data/trans_camb/P1421-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1421-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,32</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,24</t>
+          <t>3,25</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,92; 0,53</t>
+          <t>-4,4; 0,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; -0,1</t>
+          <t>-5,05; -0,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 3,59</t>
+          <t>-3,15; 2,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 8,32</t>
+          <t>-1,45; 7,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 8,72</t>
+          <t>-0,35; 8,76</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 10,33</t>
+          <t>2,22; 10,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 3,23</t>
+          <t>-1,58; 3,76</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,64</t>
+          <t>-1,59; 3,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 5,79</t>
+          <t>0,84; 5,96</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>132,67%</t>
+          <t>136,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,4; 35,49</t>
+          <t>-87,19; 77,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 17,54</t>
+          <t>-100,0; 29,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-60,39; 183,93</t>
+          <t>-66,28; 165,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-15,99; 299,72</t>
+          <t>-24,21; 283,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 296,18</t>
+          <t>-7,21; 317,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,12; 391,81</t>
+          <t>18,31; 358,52</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,48; 110,82</t>
+          <t>-33,22; 137,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-29,2; 138,29</t>
+          <t>-31,78; 131,86</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,38; 203,13</t>
+          <t>10,77; 200,48</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>5,84</t>
+          <t>5,99</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,34</t>
+          <t>5,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5,53</t>
+          <t>5,6</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,51</t>
+          <t>-1,06; 1,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 0,77</t>
+          <t>-1,44; 0,59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,18; 8,96</t>
+          <t>3,66; 9,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -0,77</t>
+          <t>-7,28; -0,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; -2,38</t>
+          <t>-8,47; -2,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,59; 9,25</t>
+          <t>1,16; 8,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; -0,07</t>
+          <t>-3,73; -0,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,59; -1,24</t>
+          <t>-4,43; -1,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,88</t>
+          <t>3,41; 8,18</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>715,97%</t>
+          <t>734,78%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>59,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>114,86%</t>
+          <t>116,36%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-99,28; 565,45</t>
+          <t>-100,0; 622,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 353,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>184,49; 2725,32</t>
+          <t>170,27; 2957,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,45; -7,08</t>
+          <t>-67,96; -6,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-77,81; -31,57</t>
+          <t>-78,29; -29,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,03; 140,13</t>
+          <t>9,35; 124,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-62,76; 1,15</t>
+          <t>-63,24; -0,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,02; -30,92</t>
+          <t>-74,9; -25,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49,85; 202,42</t>
+          <t>55,94; 209,68</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,8</t>
+          <t>2,79</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,98</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,54</t>
+          <t>5,76</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 1,31</t>
+          <t>-2,86; 1,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; -0,34</t>
+          <t>-3,77; -0,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,89</t>
+          <t>0,11; 5,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 2,99</t>
+          <t>-2,94; 2,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 2,48</t>
+          <t>-3,55; 2,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 12,24</t>
+          <t>4,7; 12,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 1,61</t>
+          <t>-2,27; 1,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 0,7</t>
+          <t>-2,9; 0,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 7,83</t>
+          <t>3,42; 8,2</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139,43%</t>
+          <t>138,88%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>189,46%</t>
+          <t>197,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>176,76%</t>
+          <t>183,73%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-84,59; 206,42</t>
+          <t>-89,2; 148,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 158,13</t>
+          <t>-100,0; 189,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 535,47</t>
+          <t>-10,6; 635,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-55,75; 105,84</t>
+          <t>-53,59; 115,86</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,12; 101,47</t>
+          <t>-61,0; 92,08</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68,63; 456,22</t>
+          <t>73,4; 471,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-53,54; 77,08</t>
+          <t>-53,06; 72,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-68,15; 36,69</t>
+          <t>-66,49; 38,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73,44; 362,96</t>
+          <t>76,47; 377,15</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,54</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,97</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1,03</t>
+          <t>1,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,83</t>
+          <t>-2,23; 1,77</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 2,12</t>
+          <t>-2,0; 1,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,84</t>
+          <t>-1,89; 2,42</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 8,57</t>
+          <t>0,93; 8,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 7,11</t>
+          <t>0,06; 7,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 3,82</t>
+          <t>-0,47; 5,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 4,58</t>
+          <t>0,43; 4,64</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,88</t>
+          <t>-0,39; 3,86</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,72</t>
+          <t>-0,42; 3,23</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>51,16%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-74,47; 268,77</t>
+          <t>-76,82; 244,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,01; 311,93</t>
+          <t>-72,58; 243,06</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-59,31; 348,29</t>
+          <t>-66,79; 338,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,25; 307,64</t>
+          <t>12,7; 282,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-9,35; 240,65</t>
+          <t>-3,73; 260,97</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-35,99; 141,95</t>
+          <t>-10,21; 194,35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 201,16</t>
+          <t>8,39; 227,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 176,05</t>
+          <t>-12,48; 179,43</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 133,66</t>
+          <t>-11,8; 145,82</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4,05</t>
+          <t>3,63</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,25</t>
+          <t>8,58</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,9</t>
+          <t>6,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,73</t>
+          <t>-2,33; 1,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 3,67</t>
+          <t>-1,81; 3,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,53</t>
+          <t>0,83; 6,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,66</t>
+          <t>2,51; 12,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 10,65</t>
+          <t>1,71; 10,4</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 12,96</t>
+          <t>4,96; 12,53</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,12</t>
+          <t>1,07; 6,29</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,94; 6,12</t>
+          <t>0,9; 5,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,36; 9,45</t>
+          <t>3,87; 8,62</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>293,45%</t>
+          <t>263,41%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>313,41%</t>
+          <t>290,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>317,38%</t>
+          <t>287,87%</t>
         </is>
       </c>
     </row>
@@ -1652,42 +1652,42 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-73,76; —</t>
+          <t>-80,94; 702,76</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8,74; 1468,77</t>
+          <t>-5,9; 1454,52</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30,02; 931,2</t>
+          <t>27,81; 845,3</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,96; 756,61</t>
+          <t>9,72; 844,69</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>71,31; 987,05</t>
+          <t>66,08; 929,25</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>28,55; 486,27</t>
+          <t>24,55; 504,27</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>20,41; 465,73</t>
+          <t>17,9; 545,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>111,36; 757,58</t>
+          <t>102,97; 724,14</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>8,58</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>5,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 1,25</t>
+          <t>-4,71; 1,16</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 1,65</t>
+          <t>-4,67; 1,55</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 6,17</t>
+          <t>-0,82; 6,23</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 2,26</t>
+          <t>-5,34; 2,26</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,29; 3,73</t>
+          <t>-4,11; 3,87</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,71; 12,86</t>
+          <t>4,19; 13,08</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-3,87; 0,72</t>
+          <t>-3,88; 0,85</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,68</t>
+          <t>-3,37; 1,67</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,77; 8,42</t>
+          <t>2,83; 8,37</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>81,72%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>139,71%</t>
+          <t>140,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>117,4%</t>
+          <t>117,29%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-86,86; 91,6</t>
+          <t>-87,38; 115,56</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 107,4</t>
+          <t>-85,48; 112,89</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-16,16; 338,13</t>
+          <t>-19,28; 351,85</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-64,09; 60,78</t>
+          <t>-63,05; 56,85</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-52,05; 88,58</t>
+          <t>-52,25; 97,33</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38,08; 299,43</t>
+          <t>43,06; 320,25</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-62,69; 27,73</t>
+          <t>-61,85; 27,24</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-57,91; 45,71</t>
+          <t>-55,63; 48,0</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42,1; 237,21</t>
+          <t>42,46; 252,21</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,87</t>
+          <t>5,6</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,99</t>
+          <t>12,92</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>7,81</t>
+          <t>9,4</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 0,97</t>
+          <t>-1,9; 0,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 2,21</t>
+          <t>-1,21; 2,08</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,36; 9,0</t>
+          <t>3,26; 8,51</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,86</t>
+          <t>-1,73; 2,86</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 4,17</t>
+          <t>-0,67; 4,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,74; 14,35</t>
+          <t>9,91; 15,8</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 1,44</t>
+          <t>-1,17; 1,4</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,64</t>
+          <t>-0,17; 2,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,83; 10,36</t>
+          <t>7,32; 11,39</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>328,86%</t>
+          <t>313,69%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>229,75%</t>
+          <t>330,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>272,3%</t>
+          <t>327,79%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-70,21; 103,03</t>
+          <t>-73,83; 98,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-43,04; 206,14</t>
+          <t>-49,8; 195,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>128,31; 817,21</t>
+          <t>122,15; 782,35</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-32,13; 108,02</t>
+          <t>-34,74; 108,34</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 140,64</t>
+          <t>-13,35; 138,76</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>41,93; 446,84</t>
+          <t>191,1; 576,13</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,85; 67,65</t>
+          <t>-33,32; 63,57</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 120,12</t>
+          <t>-6,47; 117,99</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>121,03; 450,83</t>
+          <t>197,97; 524,77</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,93</t>
+          <t>-2,6</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,82</t>
+          <t>-2,54</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-2,74</t>
+          <t>-2,58</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,06; -2,04</t>
+          <t>-5,07; -2,11</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-4,48; -1,29</t>
+          <t>-4,6; -1,35</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-4,76; -1,31</t>
+          <t>-4,19; -0,99</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-6,8; -2,13</t>
+          <t>-6,98; -2,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-6,45; -1,3</t>
+          <t>-6,0; -1,11</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,26</t>
+          <t>-5,14; -0,21</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-5,34; -2,75</t>
+          <t>-5,56; -2,67</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-4,68; -1,71</t>
+          <t>-4,88; -1,96</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-4,69; -1,1</t>
+          <t>-4,06; -1,1</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-73,82%</t>
+          <t>-65,56%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-23,56%</t>
+          <t>-32,84%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-46,45%</t>
+          <t>-43,75%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-96,9; -64,23</t>
+          <t>-96,8; -64,04</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-86,37; -38,82</t>
+          <t>-87,57; -38,82</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-91,34; -43,11</t>
+          <t>-83,84; -32,64</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-74,48; -32,56</t>
+          <t>-75,02; -36,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-69,57; -19,39</t>
+          <t>-65,53; -16,69</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-46,89; 20,18</t>
+          <t>-54,18; -3,3</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-79,18; -51,95</t>
+          <t>-79,04; -51,37</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-69,92; -35,43</t>
+          <t>-70,34; -36,72</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-68,48; -19,36</t>
+          <t>-59,05; -19,98</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2,02</t>
+          <t>2,15</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,8</t>
+          <t>5,56</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,47</t>
+          <t>3,92</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,77; -0,49</t>
+          <t>-1,83; -0,58</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,61; -0,3</t>
+          <t>-1,59; -0,28</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,06</t>
+          <t>1,26; 3,11</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 0,71</t>
+          <t>-1,51; 0,76</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 0,83</t>
+          <t>-1,48; 0,88</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,88; 6,19</t>
+          <t>4,38; 6,66</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-1,44; -0,12</t>
+          <t>-1,45; -0,12</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,15</t>
+          <t>-1,28; 0,03</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2,39; 4,48</t>
+          <t>3,2; 4,72</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>95,49%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-65,07; -22,94</t>
+          <t>-64,94; -27,81</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-59,54; -14,93</t>
+          <t>-58,43; -12,92</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>36,64; 154,57</t>
+          <t>44,88; 153,04</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-22,99; 13,71</t>
+          <t>-23,75; 15,3</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-23,12; 16,26</t>
+          <t>-23,44; 16,81</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>45,96; 117,27</t>
+          <t>65,81; 126,82</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-32,34; -3,4</t>
+          <t>-32,51; -3,11</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-27,76; 4,25</t>
+          <t>-29,17; 1,18</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>54,74; 119,5</t>
+          <t>70,81; 125,34</t>
         </is>
       </c>
     </row>
